--- a/samples/CareFlow_紙本回錄_mock範本.xlsx
+++ b/samples/CareFlow_紙本回錄_mock範本.xlsx
@@ -733,7 +733,7 @@
         <x:v>裕安樓</x:v>
       </x:c>
       <x:c r="C7" s="11" t="str">
-        <x:v>西營盤示範街 1 號（合成）</x:v>
+        <x:v>西營盤示範街 1 號</x:v>
       </x:c>
       <x:c r="D7" s="9" t="str">
         <x:v>1F：1F A室、1F B室、1F C室、1F D室
@@ -769,7 +769,7 @@
         <x:v>海景樓</x:v>
       </x:c>
       <x:c r="C8" s="12" t="str">
-        <x:v>西營盤示範街 8 號（合成）</x:v>
+        <x:v>西營盤示範街 8 號</x:v>
       </x:c>
       <x:c r="D8" s="10" t="str">
         <x:v>1F：1F A室、1F B室
@@ -799,7 +799,7 @@
         <x:v>德昌樓</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
-        <x:v>西營盤示範街 16 號（合成）</x:v>
+        <x:v>西營盤示範街 16 號</x:v>
       </x:c>
       <x:c r="D9" s="9" t="str">
         <x:v>樓層／單位未核實</x:v>
@@ -828,7 +828,7 @@
         <x:v>安和樓</x:v>
       </x:c>
       <x:c r="C10" s="12" t="str">
-        <x:v>西營盤示範街 24 號（合成）</x:v>
+        <x:v>西營盤示範街 24 號</x:v>
       </x:c>
       <x:c r="D10" s="10" t="str">
         <x:v>樓層／單位未核實</x:v>
@@ -971,7 +971,7 @@
       </x:c>
       <x:c r="C7" s="17" t="str"/>
       <x:c r="D7" s="11" t="str">
-        <x:v>西營盤示範街 1 號（合成） 5F B室</x:v>
+        <x:v>西營盤示範街 1 號 5F B室</x:v>
       </x:c>
       <x:c r="E7" s="11" t="str"/>
       <x:c r="F7" s="9" t="str">
@@ -7004,7 +7004,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B7" s="28" t="str">
-        <x:v>{"schemaVersion":"0.1-demo","isSynthetic":true,"notice":"業務資料、姓名、地址與樓層單位結構均為合成示例；占地輪廓參照 OpenStreetMap 底圖，不表示真實大廈身份或住戶資料已核實。","buildings":[{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an","name":"裕安樓","address":"西營盤示範街 1 號（合成）","layoutDeclared":true,"floorCount":8,"initialCoverage":"UNVISITED","coordinates":{"lng":114.14178818464279,"lat":22.286363930711317},"footprint":[[114.14168894290924,22.286500432351488],[114.1418981552124,22.286495468660235],[114.14189279079437,22.286227429071147],[114.14167821407318,22.286237356472498],[114.14168894290924,22.286500432351488]]},{"isSynthetic":true,"provisional":true,"id":"bldg-hoi-king","name":"海景樓","address":"西營盤示範街 8 號（合成）","layoutDeclared":true,"floorCount":2,"initialCoverage":"UNVISITED","coordinates":{"lng":114.14255797863007,"lat":22.28661211534631},"footprint":[[114.14262235164642,22.286664234063778],[114.14262235164642,22.286619560888553],[114.14259016513824,22.286624524575387],[114.14258480072021,22.286589778763798],[114.14263308048248,22.286589778763798],[114.14263308048248,22.286555032943582],[114.14248287677765,22.286559996632704],[114.14248287677765,22.28659474245171],[114.14253115653992,22.28659474245171],[114.14253115653992,22.286624524575387],[114.14249897003174,22.286624524575387],[114.14249897003174,22.286669197749035],[114.14262235164642,22.286664234063778]]},{"isSynthetic":true,"provisional":true,"id":"bldg-duk-cheong","name":"德昌樓","address":"西營盤示範街 16 號（合成）","layoutDeclared":false,"initialCoverage":"UNKNOWN","coordinates":{"lng":114.14136976003647,"lat":22.286808180844794},"footprint":[[114.1414475440979,22.286733725641312],[114.14129197597504,22.286733725641312],[114.14129197597504,22.286882636048276],[114.1414475440979,22.286877672370593],[114.1414475440979,22.286733725641312]]},{"isSynthetic":true,"provisional":true,"id":"bldg-on-wo","name":"安和樓","address":"西營盤示範街 24 號（合成）","layoutDeclared":false,"initialCoverage":"UNKNOWN","coordinates":{"lng":114.14208590984344,"lat":22.28576580411479},"footprint":[[114.14213418960571,22.285825368723906],[114.14212882518768,22.28570127579063],[114.14203763008118,22.285706239510063],[114.1420429944992,22.285830332438948],[114.14213418960571,22.285825368723906]]}],"floors":[{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f1","buildingId":"bldg-yu-an","label":"1F","level":1},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f2","buildingId":"bldg-yu-an","label":"2F","level":2},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f3","buildingId":"bldg-yu-an","label":"3F","level":3},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f4","buildingId":"bldg-yu-an","label":"4F","level":4},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f5","buildingId":"bldg-yu-an","label":"5F","level":5},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f6","buildingId":"bldg-yu-an","label":"6F","level":6},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f7","buildingId":"bldg-yu-an","label":"7F","level":7},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f8","buildingId":"bldg-yu-an","label":"8F","level":8},{"isSynthetic":true,"provisional":true,"id":"bldg-hoi-king-f1","buildingId":"bldg-hoi-king","label":"1F","level":1},{"isSynthetic":true,"provisional":true,"id":"bldg-hoi-king-f2","buildingId":"bldg-hoi-king","label":"2F","level":2}],"units":[{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f1-A","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f1","label":"1F A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f1-B","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f1","label":"1F B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f1-C","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f1","label":"1F C室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f1-D","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f1","label":"1F D室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f2-A","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f2","label":"2F A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f2-B","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f2","label":"2F B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f2-C","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f2","label":"2F C室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f2-D","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f2","label":"2F D室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f3-A","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f3","label":"3F A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f3-B","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f3","label":"3F B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f3-C","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f3","label":"3F C室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f3-D","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f3","label":"3F D室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f4-A","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f4","label":"4F A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f4-B","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f4","label":"4F B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f4-C","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f4","label":"4F C室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f4-D","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f4","label":"4F D室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f5-A","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f5","label":"5F A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f5-B","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f5","label":"5F B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f5-C","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f5","label":"5F C室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f5-D","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f5","label":"5F D室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f6-A","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f6","label":"6F A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f6-B","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f6","label":"6F B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f6-C","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f6","label":"6F C室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f6-D","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f6","label":"6F D室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f7-A","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f7","label":"7F A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f7-B","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f7","label":"7F B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f7-C","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f7","label":"7F C室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f7-D","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f7","label":"7F D室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f8-A","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f8","label":"8F A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f8-B","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f8","label":"8F B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f8-C","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f8","label":"8F C室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f8-D","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f8","label":"8F D室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-hoi-king-f1-A","buildingId":"bldg-hoi-king","floorId":"bldg-hoi-king-f1","label":"1F A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-hoi-king-f1-B","buildingId":"bldg-hoi-king","floorId":"bldg-hoi-king-f1","label":"1F B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-hoi-king-f2-A","buildingId":"bldg-hoi-king","floorId":"bldg-hoi-king-f2","label":"2F A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-hoi-king-f2-B","buildingId":"bldg-hoi-king","floorId":"bldg-hoi-king-f2","label":"2F B室","initialCoverage":"UNVISITED"}],"households":[{"isSynthetic":true,"provisional":true,"id":"household-lam","label":"林家庭（合成）"}],"people":[{"isSynthetic":true,"provisional":true,"id":"person-lam","displayName":"林女士（合成）"},{"isSynthetic":true,"provisional":true,"id":"person-chan","displayName":"陳先生（合成）"}],"householdMemberships":[{"isSynthetic":true,"provisional":true,"id":"hhm-lam","householdId":"household-lam","personId":"person-lam","relationship":"戶主（合成）"}],"householdResidences":[{"isSynthetic":true,"provisional":true,"id":"residence-lam","householdId":"household-lam","buildingId":"bldg-yu-an","unitId":"bldg-yu-an-f5-B","startsOn":"2026-09-01"}],"memberships":[{"isSynthetic":true,"provisional":true,"id":"membership-lam","personId":"person-lam","status":"PENDING"}],"visits":[{"isSynthetic":true,"provisional":true,"id":"visit-yu-an-2026-09-09","occurredAt":"2026-09-09T18:30:00+08:00","recordedAt":"2026-09-09T20:15:00+08:00","workerName":"示範工作員甲（合成）","note":"合成示例：同一次外出可以寫入多個位置。"},{"isSynthetic":true,"provisional":true,"id":"visit-hoi-king-2026-09-08","occurredAt":"2026-09-08T18:30:00+08:00","recordedAt":"2026-09-08T20:15:00+08:00","workerName":"示範工作員乙（合成）"},{"isSynthetic":true,"provisional":true,"id":"visit-duk-cheong-2026-09-07","occurredAt":"2026-09-07T18:30:00+08:00","recordedAt":"2026-09-07T20:15:00+08:00","workerName":"示範工作員丙（合成）"},{"isSynthetic":true,"provisional":true,"id":"demo-paper-visit-0910","occurredAt":"2026-09-10","recordedAt":"2026-09-11T09:00:00+08:00","workerName":"演示工作員乙"}],"observations":[{"isSynthetic":true,"provisional":true,"id":"observation-yu-an-5b","visitId":"visit-yu-an-2026-09-09","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f5","unitId":"bldg-yu-an-f5-B","occurredAt":"2026-09-09T18:40:00+08:00","recordedAt":"2026-09-09T20:15:00+08:00","workerName":"示範工作員甲（合成）","coverage":"ATTEMPTED","assessment":"SUSPECTED","contactOutcome":"NO_ANSWER","sourceType":"STAFF_OBSERVATION","note":"敲門兩次，未有人應門。信箱有細分標籤，住房情況仍需向住戶核實。","evidence":["信箱細分為 B1、B2","門外可見多個空調外機"],"followUp":{"action":"傍晚再次到訪，了解服務需要","dueDate":"2026-09-16","status":"OPEN"}},{"isSynthetic":true,"provisional":true,"id":"observation-yu-an-5a","visitId":"visit-yu-an-2026-09-09","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f5","unitId":"bldg-yu-an-f5-A","occurredAt":"2026-09-09T18:39:00+08:00","recordedAt":"2026-09-09T20:14:00+08:00","workerName":"示範工作員甲（合成）","coverage":"VISITED_NO_FINDING","assessment":"NO_INDICATION","contactOutcome":"CONTACTED","evidence":[]},{"isSynthetic":true,"provisional":true,"id":"observation-yu-an-5c","visitId":"visit-yu-an-2026-09-09","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f5","unitId":"bldg-yu-an-f5-C","occurredAt":"2026-09-09T18:38:00+08:00","recordedAt":"2026-09-09T20:13:00+08:00","workerName":"示範工作員甲（合成）","coverage":"UNKNOWN","note":"舊表未寫明是否已查看，先保留未知，待工作員核對。","evidence":[]},{"isSynthetic":true,"provisional":true,"id":"observation-yu-an-5d","visitId":"visit-yu-an-2026-09-09","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f5","unitId":"bldg-yu-an-f5-D","occurredAt":"2026-09-09T18:37:00+08:00","recordedAt":"2026-09-09T20:12:00+08:00","workerName":"示範工作員甲（合成）","coverage":"VISITED_WITH_FINDING","assessment":"SUSPECTED","contactOutcome":"DECLINED","evidence":["合成示例：需由工作員後續核實。"]},{"isSynthetic":true,"provisional":true,"id":"observation-bldg-yu-an-f1-A","visitId":"visit-yu-an-2026-09-09","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f1","unitId":"bldg-yu-an-f1-A","occurredAt":"2026-09-09T19:10:00+08:00","recordedAt":"2026-09-09T20:10:00+08:00","workerName":"示範工作員甲（合成）","coverage":"PARTIAL","assessment":"NOT_UPDATED","contactOutcome":"UNKNOWN","evidence":[]},{"isSynthetic":true,"provisional":true,"id":"observation-bldg-yu-an-f1-B","visitId":"visit-yu-an-2026-09-09","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f1","unitId":"bldg-yu-an-f1-B","occurredAt":"2026-09-09T19:11:00+08:00","recordedAt":"2026-09-09T20:11:00+08:00","workerName":"示範工作員甲（合成）","coverage":"VISITED_NO_FINDING","assessment":"NO_INDICATION","contactOutcome":"CONTACTED","evidence":[]},{"isSynthetic":true,"provisional":true,"id":"observation-bldg-yu-an-f1-C","visitId":"visit-yu-an-2026-09-09","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f1","unitId":"bldg-yu-an-f1-C","occurredAt":"2026-09-09T19:12:00+08:00","recordedAt":"2026-09-09T20:12:00+08:00","workerName":"示範工作員甲（合成）","coverage":"VISITED_NO_FINDING","assessment":"NO_INDICATION","contactOutcome":"CONTACTED","evidence":[]},{"isSynthetic":true,"provisional":true,"id":"observation-bldg-yu-an-f1-D","visitId":"visit-yu-an-2026-09-09","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f1","unitId":"bldg-yu-an-f1-D","occurredAt":"2026-09-09T19:13:00+08:00","recordedAt":"2026-09-09T20:13:00+08:00","workerName":"示範工作員甲（合成）","coverage":"VISITED_NO_FINDING","assessment":"NO_INDICATION","contactOutcome":"CONTACTED","evidence":[]},{"isSynthetic":true,"provisional":true,"id":"observation-bldg-yu-an-f2-A","visitId":"visit-yu-an-2026-09-09","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f2","unitId":"bldg-yu-an-f2-A","occurredAt":"2026-09-09T19:14:00+08:00","recordedAt":"2026-09-09T20:14:00+08:00","workerName":"示範工作員甲（合成）","coverage":"VISITED_NO_FINDING","assessment":"NO_INDICATION","contactOutcome":"CONTACTED","evidence":[]},{"isSynthetic":true,"provisional":true,"id":"observation-bldg-yu-an-f2-B","visitId":"visit-yu-an-2026-09-09","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f2","unitId":"bldg-yu-an-f2-B","occurredAt":"2026-09-09T19:15:00+08:00","recordedAt":"2026-09-09T20:15:00+08:00","workerName":"示範工作員甲（合成）","coverage":"PARTIAL","assessment":"NOT_UPDATED","contactOutcome":"UNKNOWN","evidence":[]},{"isSynthetic":true,"provisional":true,"id":"observation-bldg-yu-an-f2-C","visitId":"visit-yu-an-2026-09-09","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f2","unitId":"bldg-yu-an-f2-C","occurredAt":"2026-09-09T19:16:00+08:00","recordedAt":"2026-09-09T20:16:00+08:00","workerName":"示範工作員甲（合成）","coverage":"VISITED_NO_FINDING","assessment":"NO_INDICATION","contactOutcome":"CONTACTED","evidence":[]},{"isSynthetic":true,"provisional":true,"id":"observation-bldg-yu-an-f2-D","visitId":"visit-yu-an-2026-09-09","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f2","unitId":"bldg-yu-an-f2-D","occurredAt":"2026-09-09T19:17:00+08:00","recordedAt":"2026-09-09T20:17:00+08:00","workerName":"示範工作員甲（合成）","coverage":"VISITED_NO_FINDING","assessment":"NO_INDICATION","contactOutcome":"CONTACTED","evidence":[]},{"isSynthetic":true,"provisional":true,"id":"observation-bldg-yu-an-f3-A","visitId":"visit-yu-an-2026-09-09","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f3","unitId":"bldg-yu-an-f3-A","occurredAt":"2026-09-09T19:18:00+08:00","recordedAt":"2026-09-09T20:18:00+08:00","workerName":"示範工作員甲（合成）","coverage":"VISITED_NO_FINDING","assessment":"NO_INDICATION","contactOutcome":"CONTACTED","evidence":[]},{"isSynthetic":true,"provisional":true,"id":"observation-bldg-yu-an-f3-B","visitId":"visit-yu-an-2026-09-09","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f3","unitId":"bldg-yu-an-f3-B","occurredAt":"2026-09-09T19:19:00+08:00","recordedAt":"2026-09-09T20:19:00+08:00","workerName":"示範工作員甲（合成）","coverage":"VISITED_NO_FINDING","assessment":"NO_INDICATION","contactOutcome":"CONTACTED","evidence":[]},{"isSynthetic":true,"provisional":true,"id":"observation-bldg-yu-an-f3-C","visitId":"visit-yu-an-2026-09-09","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f3","unitId":"bldg-yu-an-f3-C","occurredAt":"2026-09-09T19:20:00+08:00","recordedAt":"2026-09-09T20:20:00+08:00","workerName":"示範工作員甲（合成）","coverage":"PARTIAL","assessment":"NOT_UPDATED","contactOutcome":"UNKNOWN","evidence":[]},{"isSynthetic":true,"provisional":true,"id":"observation-bldg-yu-an-f3-D","visitId":"visit-yu-an-2026-09-09","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f3","unitId":"bldg-yu-an-f3-D","occurredAt":"2026-09-09T19:21:00+08:00","recordedAt":"2026-09-09T20:21:00+08:00","workerName":"示範工作員甲（合成）","coverage":"VISITED_NO_FINDING","assessment":"NO_INDICATION","contactOutcome":"CONTACTED","evidence":[]},{"isSynthetic":true,"provisional":true,"id":"observation-bldg-yu-an-f4-A","visitId":"visit-yu-an-2026-09-09","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f4","unitId":"bldg-yu-an-f4-A","occurredAt":"2026-09-09T19:22:00+08:00","recordedAt":"2026-09-09T20:22:00+08:00","workerName":"示範工作員甲（合成）","coverage":"VISITED_NO_FINDING","assessment":"NO_INDICATION","contactOutcome":"CONTACTED","evidence":[]},{"isSynthetic":true,"provisional":true,"id":"observation-bldg-yu-an-f4-B","visitId":"visit-yu-an-2026-09-09","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f4","unitId":"bldg-yu-an-f4-B","occurredAt":"2026-09-09T19:23:00+08:00","recordedAt":"2026-09-09T20:23:00+08:00","workerName":"示範工作員甲（合成）","coverage":"VISITED_NO_FINDING","assessment":"NO_INDICATION","contactOutcome":"CONTACTED","evidence":[]},{"isSynthetic":true,"provisional":true,"id":"observation-bldg-yu-an-f4-C","visitId":"visit-yu-an-2026-09-09","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f4","unitId":"bldg-yu-an-f4-C","occurredAt":"2026-09-09T19:24:00+08:00","recordedAt":"2026-09-09T20:24:00+08:00","workerName":"示範工作員甲（合成）","coverage":"VISITED_NO_FINDING","assessment":"NO_INDICATION","contactOutcome":"CONTACTED","evidence":[]},{"isSynthetic":true,"provisional":true,"id":"observation-bldg-yu-an-f4-D","visitId":"visit-yu-an-2026-09-09","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f4","unitId":"bldg-yu-an-f4-D","occurredAt":"2026-09-09T19:25:00+08:00","recordedAt":"2026-09-09T20:25:00+08:00","workerName":"示範工作員甲（合成）","coverage":"PARTIAL","assessment":"NOT_UPDATED","contactOutcome":"UNKNOWN","evidence":[]},{"isSynthetic":true,"provisional":true,"id":"observation-bldg-yu-an-f6-A","visitId":"visit-yu-an-2026-09-09","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f6","unitId":"bldg-yu-an-f6-A","occurredAt":"2026-09-09T19:26:00+08:00","recordedAt":"2026-09-09T20:26:00+08:00","workerName":"示範工作員甲（合成）","coverage":"VISITED_NO_FINDING","assessment":"NO_INDICATION","contactOutcome":"CONTACTED","evidence":[]},{"isSynthetic":true,"provisional":true,"id":"observation-bldg-yu-an-f6-B","visitId":"visit-yu-an-2026-09-09","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f6","unitId":"bldg-yu-an-f6-B","occurredAt":"2026-09-09T19:27:00+08:00","recordedAt":"2026-09-09T20:27:00+08:00","workerName":"示範工作員甲（合成）","coverage":"VISITED_NO_FINDING","assessment":"NO_INDICATION","contactOutcome":"CONTACTED","evidence":[]},{"isSynthetic":true,"provisional":true,"id":"observation-hoi-king-2a","visitId":"visit-hoi-king-2026-09-08","buildingId":"bldg-hoi-king","floorId":"bldg-hoi-king-f2","unitId":"bldg-hoi-king-f2-A","occurredAt":"2026-09-08T18:45:00+08:00","recordedAt":"2026-09-08T20:15:00+08:00","workerName":"示範工作員乙（合成）","coverage":"VISITED_NO_FINDING","assessment":"NOT_UPDATED","contactOutcome":"CONTACTED","evidence":[],"note":"合成示例：已探訪但本次未記錄發現。"},{"isSynthetic":true,"provisional":true,"id":"observation-hoi-king-2b","visitId":"visit-hoi-king-2026-09-08","buildingId":"bldg-hoi-king","floorId":"bldg-hoi-king-f2","unitId":"bldg-hoi-king-f2-B","occurredAt":"2026-09-08T18:44:00+08:00","recordedAt":"2026-09-08T20:14:00+08:00","workerName":"示範工作員乙（合成）","coverage":"VISITED_NO_FINDING","assessment":"NO_INDICATION","contactOutcome":"CONTACTED","evidence":[]},{"isSynthetic":true,"provisional":true,"id":"observation-duk-cheong-entry","visitId":"visit-duk-cheong-2026-09-07","buildingId":"bldg-duk-cheong","occurredAt":"2026-09-07T18:45:00+08:00","recordedAt":"2026-09-07T20:15:00+08:00","workerName":"示範工作員丙（合成）","coverage":"INACCESSIBLE","contactOutcome":"NOT_ATTEMPTED","evidence":["合成示例：入口未能進入。"],"followUp":{"action":"合成示例：與同事討論是否再訪","status":"OPEN"}},{"isSynthetic":true,"provisional":true,"id":"demo-paper-housing","visitId":"demo-paper-visit-0910","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f5","unitId":"bldg-yu-an-f5-B","occurredAt":"2026-09-10","recordedAt":"2026-09-11T09:00:00+08:00","workerName":"演示工作員乙","coverage":"ATTEMPTED","contactOutcome":"CONTACTED","assessment":"NOT_UPDATED","sourceType":"RESIDENT_REPORT","note":"合成示例：住戶表示業主可能收回單位。具體安排和通知日期未確認。","evidence":["合成居民口述，未見書面通知"],"paperRef":"DEMO-0910-01","paperLine":"1","followUp":{"action":"再聯絡住戶，確認搬遷安排及需要的住屋支援","status":"OPEN","category":"HOUSING_CHANGE","assignee":"演示工作員乙","timingNote":"「明年二月」為示範原話，年份及日期待核實"}},{"isSynthetic":true,"provisional":true,"id":"demo-paper-health","visitId":"demo-paper-visit-0910","buildingId":"bldg-hoi-king","occurredAt":"2026-09-10","recordedAt":"2026-09-11T09:05:00+08:00","workerName":"演示工作員乙","coverage":"PARTIAL","contactOutcome":"CONTACTED","assessment":"NOT_UPDATED","sourceType":"RESIDENT_REPORT","note":"合成示例：街坊提到腳部不適及走路困難。只記錄表述，不推定病名。","evidence":["合成居民口述"],"paperRef":"DEMO-0910-02","paperLine":"1","followUp":{"action":"聯絡中心護士同事，確認可提供的關懷安排","status":"OPEN","category":"HEALTH_SUPPORT","assignee":"演示工作員乙","timingNote":"翌日午後（實際日期及到場安排待確認）"}},{"isSynthetic":true,"provisional":true,"id":"demo-paper-invite","visitId":"demo-paper-visit-0910","buildingId":"bldg-hoi-king","occurredAt":"2026-09-10","recordedAt":"2026-09-11T09:10:00+08:00","workerName":"演示工作員乙","coverage":"PARTIAL","contactOutcome":"CONTACTED","assessment":"NOT_UPDATED","sourceType":"STAFF_OBSERVATION","note":"合成示例：已介紹社區客廳服務，街坊有興趣了解；未表示已入會。","evidence":[],"paperRef":"DEMO-0910-02","paperLine":"2","followUp":{"action":"確認街坊到訪意願及是否需要協助前來","status":"OPEN","category":"SERVICE_INVITATION","timingNote":"有口頭邀約，未確認到場"}}]}</x:v>
+        <x:v>{"schemaVersion":"0.1-demo","isSynthetic":true,"notice":"業務資料、姓名、地址與樓層單位結構均為合成示例；占地輪廓參照 OpenStreetMap 底圖，不表示真實大廈身份或住戶資料已核實。","buildings":[{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an","name":"裕安樓","address":"西營盤示範街 1 號","layoutDeclared":true,"floorCount":8,"initialCoverage":"UNVISITED","coordinates":{"lng":114.14178818464279,"lat":22.286363930711317},"footprint":[[114.14168894290924,22.286500432351488],[114.1418981552124,22.286495468660235],[114.14189279079437,22.286227429071147],[114.14167821407318,22.286237356472498],[114.14168894290924,22.286500432351488]]},{"isSynthetic":true,"provisional":true,"id":"bldg-hoi-king","name":"海景樓","address":"西營盤示範街 8 號","layoutDeclared":true,"floorCount":2,"initialCoverage":"UNVISITED","coordinates":{"lng":114.14255797863007,"lat":22.28661211534631},"footprint":[[114.14262235164642,22.286664234063778],[114.14262235164642,22.286619560888553],[114.14259016513824,22.286624524575387],[114.14258480072021,22.286589778763798],[114.14263308048248,22.286589778763798],[114.14263308048248,22.286555032943582],[114.14248287677765,22.286559996632704],[114.14248287677765,22.28659474245171],[114.14253115653992,22.28659474245171],[114.14253115653992,22.286624524575387],[114.14249897003174,22.286624524575387],[114.14249897003174,22.286669197749035],[114.14262235164642,22.286664234063778]]},{"isSynthetic":true,"provisional":true,"id":"bldg-duk-cheong","name":"德昌樓","address":"西營盤示範街 16 號","layoutDeclared":false,"initialCoverage":"UNKNOWN","coordinates":{"lng":114.14136976003647,"lat":22.286808180844794},"footprint":[[114.1414475440979,22.286733725641312],[114.14129197597504,22.286733725641312],[114.14129197597504,22.286882636048276],[114.1414475440979,22.286877672370593],[114.1414475440979,22.286733725641312]]},{"isSynthetic":true,"provisional":true,"id":"bldg-on-wo","name":"安和樓","address":"西營盤示範街 24 號","layoutDeclared":false,"initialCoverage":"UNKNOWN","coordinates":{"lng":114.14208590984344,"lat":22.28576580411479},"footprint":[[114.14213418960571,22.285825368723906],[114.14212882518768,22.28570127579063],[114.14203763008118,22.285706239510063],[114.1420429944992,22.285830332438948],[114.14213418960571,22.285825368723906]]}],"floors":[{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f1","buildingId":"bldg-yu-an","label":"1F","level":1},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f2","buildingId":"bldg-yu-an","label":"2F","level":2},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f3","buildingId":"bldg-yu-an","label":"3F","level":3},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f4","buildingId":"bldg-yu-an","label":"4F","level":4},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f5","buildingId":"bldg-yu-an","label":"5F","level":5},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f6","buildingId":"bldg-yu-an","label":"6F","level":6},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f7","buildingId":"bldg-yu-an","label":"7F","level":7},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f8","buildingId":"bldg-yu-an","label":"8F","level":8},{"isSynthetic":true,"provisional":true,"id":"bldg-hoi-king-f1","buildingId":"bldg-hoi-king","label":"1F","level":1},{"isSynthetic":true,"provisional":true,"id":"bldg-hoi-king-f2","buildingId":"bldg-hoi-king","label":"2F","level":2}],"units":[{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f1-A","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f1","label":"1F A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f1-B","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f1","label":"1F B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f1-C","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f1","label":"1F C室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f1-D","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f1","label":"1F D室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f2-A","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f2","label":"2F A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f2-B","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f2","label":"2F B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f2-C","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f2","label":"2F C室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f2-D","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f2","label":"2F D室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f3-A","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f3","label":"3F A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f3-B","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f3","label":"3F B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f3-C","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f3","label":"3F C室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f3-D","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f3","label":"3F D室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f4-A","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f4","label":"4F A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f4-B","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f4","label":"4F B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f4-C","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f4","label":"4F C室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f4-D","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f4","label":"4F D室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f5-A","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f5","label":"5F A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f5-B","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f5","label":"5F B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f5-C","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f5","label":"5F C室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f5-D","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f5","label":"5F D室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f6-A","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f6","label":"6F A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f6-B","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f6","label":"6F B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f6-C","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f6","label":"6F C室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f6-D","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f6","label":"6F D室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f7-A","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f7","label":"7F A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f7-B","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f7","label":"7F B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f7-C","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f7","label":"7F C室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f7-D","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f7","label":"7F D室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f8-A","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f8","label":"8F A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f8-B","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f8","label":"8F B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f8-C","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f8","label":"8F C室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-yu-an-f8-D","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f8","label":"8F D室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-hoi-king-f1-A","buildingId":"bldg-hoi-king","floorId":"bldg-hoi-king-f1","label":"1F A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-hoi-king-f1-B","buildingId":"bldg-hoi-king","floorId":"bldg-hoi-king-f1","label":"1F B室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-hoi-king-f2-A","buildingId":"bldg-hoi-king","floorId":"bldg-hoi-king-f2","label":"2F A室","initialCoverage":"UNVISITED"},{"isSynthetic":true,"provisional":true,"id":"bldg-hoi-king-f2-B","buildingId":"bldg-hoi-king","floorId":"bldg-hoi-king-f2","label":"2F B室","initialCoverage":"UNVISITED"}],"households":[{"isSynthetic":true,"provisional":true,"id":"household-lam","label":"林家庭（合成）"}],"people":[{"isSynthetic":true,"provisional":true,"id":"person-lam","displayName":"林女士（合成）"},{"isSynthetic":true,"provisional":true,"id":"person-chan","displayName":"陳先生（合成）"}],"householdMemberships":[{"isSynthetic":true,"provisional":true,"id":"hhm-lam","householdId":"household-lam","personId":"person-lam","relationship":"戶主（合成）"}],"householdResidences":[{"isSynthetic":true,"provisional":true,"id":"residence-lam","householdId":"household-lam","buildingId":"bldg-yu-an","unitId":"bldg-yu-an-f5-B","startsOn":"2026-09-01"}],"memberships":[{"isSynthetic":true,"provisional":true,"id":"membership-lam","personId":"person-lam","status":"PENDING"}],"visits":[{"isSynthetic":true,"provisional":true,"id":"visit-yu-an-2026-09-09","occurredAt":"2026-09-09T18:30:00+08:00","recordedAt":"2026-09-09T20:15:00+08:00","workerName":"示範工作員甲（合成）","note":"合成示例：同一次外出可以寫入多個位置。"},{"isSynthetic":true,"provisional":true,"id":"visit-hoi-king-2026-09-08","occurredAt":"2026-09-08T18:30:00+08:00","recordedAt":"2026-09-08T20:15:00+08:00","workerName":"示範工作員乙（合成）"},{"isSynthetic":true,"provisional":true,"id":"visit-duk-cheong-2026-09-07","occurredAt":"2026-09-07T18:30:00+08:00","recordedAt":"2026-09-07T20:15:00+08:00","workerName":"示範工作員丙（合成）"},{"isSynthetic":true,"provisional":true,"id":"demo-paper-visit-0910","occurredAt":"2026-09-10","recordedAt":"2026-09-11T09:00:00+08:00","workerName":"演示工作員乙"}],"observations":[{"isSynthetic":true,"provisional":true,"id":"observation-yu-an-5b","visitId":"visit-yu-an-2026-09-09","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f5","unitId":"bldg-yu-an-f5-B","occurredAt":"2026-09-09T18:40:00+08:00","recordedAt":"2026-09-09T20:15:00+08:00","workerName":"示範工作員甲（合成）","coverage":"ATTEMPTED","assessment":"SUSPECTED","contactOutcome":"NO_ANSWER","sourceType":"STAFF_OBSERVATION","note":"敲門兩次，未有人應門。信箱有細分標籤，住房情況仍需向住戶核實。","evidence":["信箱細分為 B1、B2","門外可見多個空調外機"],"followUp":{"action":"傍晚再次到訪，了解服務需要","dueDate":"2026-09-16","status":"OPEN"}},{"isSynthetic":true,"provisional":true,"id":"observation-yu-an-5a","visitId":"visit-yu-an-2026-09-09","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f5","unitId":"bldg-yu-an-f5-A","occurredAt":"2026-09-09T18:39:00+08:00","recordedAt":"2026-09-09T20:14:00+08:00","workerName":"示範工作員甲（合成）","coverage":"VISITED_NO_FINDING","assessment":"NO_INDICATION","contactOutcome":"CONTACTED","evidence":[]},{"isSynthetic":true,"provisional":true,"id":"observation-yu-an-5c","visitId":"visit-yu-an-2026-09-09","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f5","unitId":"bldg-yu-an-f5-C","occurredAt":"2026-09-09T18:38:00+08:00","recordedAt":"2026-09-09T20:13:00+08:00","workerName":"示範工作員甲（合成）","coverage":"UNKNOWN","note":"舊表未寫明是否已查看，先保留未知，待工作員核對。","evidence":[]},{"isSynthetic":true,"provisional":true,"id":"observation-yu-an-5d","visitId":"visit-yu-an-2026-09-09","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f5","unitId":"bldg-yu-an-f5-D","occurredAt":"2026-09-09T18:37:00+08:00","recordedAt":"2026-09-09T20:12:00+08:00","workerName":"示範工作員甲（合成）","coverage":"VISITED_WITH_FINDING","assessment":"SUSPECTED","contactOutcome":"DECLINED","evidence":["合成示例：需由工作員後續核實。"]},{"isSynthetic":true,"provisional":true,"id":"observation-bldg-yu-an-f1-A","visitId":"visit-yu-an-2026-09-09","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f1","unitId":"bldg-yu-an-f1-A","occurredAt":"2026-09-09T19:10:00+08:00","recordedAt":"2026-09-09T20:10:00+08:00","workerName":"示範工作員甲（合成）","coverage":"PARTIAL","assessment":"NOT_UPDATED","contactOutcome":"UNKNOWN","evidence":[]},{"isSynthetic":true,"provisional":true,"id":"observation-bldg-yu-an-f1-B","visitId":"visit-yu-an-2026-09-09","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f1","unitId":"bldg-yu-an-f1-B","occurredAt":"2026-09-09T19:11:00+08:00","recordedAt":"2026-09-09T20:11:00+08:00","workerName":"示範工作員甲（合成）","coverage":"VISITED_NO_FINDING","assessment":"NO_INDICATION","contactOutcome":"CONTACTED","evidence":[]},{"isSynthetic":true,"provisional":true,"id":"observation-bldg-yu-an-f1-C","visitId":"visit-yu-an-2026-09-09","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f1","unitId":"bldg-yu-an-f1-C","occurredAt":"2026-09-09T19:12:00+08:00","recordedAt":"2026-09-09T20:12:00+08:00","workerName":"示範工作員甲（合成）","coverage":"VISITED_NO_FINDING","assessment":"NO_INDICATION","contactOutcome":"CONTACTED","evidence":[]},{"isSynthetic":true,"provisional":true,"id":"observation-bldg-yu-an-f1-D","visitId":"visit-yu-an-2026-09-09","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f1","unitId":"bldg-yu-an-f1-D","occurredAt":"2026-09-09T19:13:00+08:00","recordedAt":"2026-09-09T20:13:00+08:00","workerName":"示範工作員甲（合成）","coverage":"VISITED_NO_FINDING","assessment":"NO_INDICATION","contactOutcome":"CONTACTED","evidence":[]},{"isSynthetic":true,"provisional":true,"id":"observation-bldg-yu-an-f2-A","visitId":"visit-yu-an-2026-09-09","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f2","unitId":"bldg-yu-an-f2-A","occurredAt":"2026-09-09T19:14:00+08:00","recordedAt":"2026-09-09T20:14:00+08:00","workerName":"示範工作員甲（合成）","coverage":"VISITED_NO_FINDING","assessment":"NO_INDICATION","contactOutcome":"CONTACTED","evidence":[]},{"isSynthetic":true,"provisional":true,"id":"observation-bldg-yu-an-f2-B","visitId":"visit-yu-an-2026-09-09","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f2","unitId":"bldg-yu-an-f2-B","occurredAt":"2026-09-09T19:15:00+08:00","recordedAt":"2026-09-09T20:15:00+08:00","workerName":"示範工作員甲（合成）","coverage":"PARTIAL","assessment":"NOT_UPDATED","contactOutcome":"UNKNOWN","evidence":[]},{"isSynthetic":true,"provisional":true,"id":"observation-bldg-yu-an-f2-C","visitId":"visit-yu-an-2026-09-09","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f2","unitId":"bldg-yu-an-f2-C","occurredAt":"2026-09-09T19:16:00+08:00","recordedAt":"2026-09-09T20:16:00+08:00","workerName":"示範工作員甲（合成）","coverage":"VISITED_NO_FINDING","assessment":"NO_INDICATION","contactOutcome":"CONTACTED","evidence":[]},{"isSynthetic":true,"provisional":true,"id":"observation-bldg-yu-an-f2-D","visitId":"visit-yu-an-2026-09-09","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f2","unitId":"bldg-yu-an-f2-D","occurredAt":"2026-09-09T19:17:00+08:00","recordedAt":"2026-09-09T20:17:00+08:00","workerName":"示範工作員甲（合成）","coverage":"VISITED_NO_FINDING","assessment":"NO_INDICATION","contactOutcome":"CONTACTED","evidence":[]},{"isSynthetic":true,"provisional":true,"id":"observation-bldg-yu-an-f3-A","visitId":"visit-yu-an-2026-09-09","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f3","unitId":"bldg-yu-an-f3-A","occurredAt":"2026-09-09T19:18:00+08:00","recordedAt":"2026-09-09T20:18:00+08:00","workerName":"示範工作員甲（合成）","coverage":"VISITED_NO_FINDING","assessment":"NO_INDICATION","contactOutcome":"CONTACTED","evidence":[]},{"isSynthetic":true,"provisional":true,"id":"observation-bldg-yu-an-f3-B","visitId":"visit-yu-an-2026-09-09","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f3","unitId":"bldg-yu-an-f3-B","occurredAt":"2026-09-09T19:19:00+08:00","recordedAt":"2026-09-09T20:19:00+08:00","workerName":"示範工作員甲（合成）","coverage":"VISITED_NO_FINDING","assessment":"NO_INDICATION","contactOutcome":"CONTACTED","evidence":[]},{"isSynthetic":true,"provisional":true,"id":"observation-bldg-yu-an-f3-C","visitId":"visit-yu-an-2026-09-09","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f3","unitId":"bldg-yu-an-f3-C","occurredAt":"2026-09-09T19:20:00+08:00","recordedAt":"2026-09-09T20:20:00+08:00","workerName":"示範工作員甲（合成）","coverage":"PARTIAL","assessment":"NOT_UPDATED","contactOutcome":"UNKNOWN","evidence":[]},{"isSynthetic":true,"provisional":true,"id":"observation-bldg-yu-an-f3-D","visitId":"visit-yu-an-2026-09-09","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f3","unitId":"bldg-yu-an-f3-D","occurredAt":"2026-09-09T19:21:00+08:00","recordedAt":"2026-09-09T20:21:00+08:00","workerName":"示範工作員甲（合成）","coverage":"VISITED_NO_FINDING","assessment":"NO_INDICATION","contactOutcome":"CONTACTED","evidence":[]},{"isSynthetic":true,"provisional":true,"id":"observation-bldg-yu-an-f4-A","visitId":"visit-yu-an-2026-09-09","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f4","unitId":"bldg-yu-an-f4-A","occurredAt":"2026-09-09T19:22:00+08:00","recordedAt":"2026-09-09T20:22:00+08:00","workerName":"示範工作員甲（合成）","coverage":"VISITED_NO_FINDING","assessment":"NO_INDICATION","contactOutcome":"CONTACTED","evidence":[]},{"isSynthetic":true,"provisional":true,"id":"observation-bldg-yu-an-f4-B","visitId":"visit-yu-an-2026-09-09","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f4","unitId":"bldg-yu-an-f4-B","occurredAt":"2026-09-09T19:23:00+08:00","recordedAt":"2026-09-09T20:23:00+08:00","workerName":"示範工作員甲（合成）","coverage":"VISITED_NO_FINDING","assessment":"NO_INDICATION","contactOutcome":"CONTACTED","evidence":[]},{"isSynthetic":true,"provisional":true,"id":"observation-bldg-yu-an-f4-C","visitId":"visit-yu-an-2026-09-09","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f4","unitId":"bldg-yu-an-f4-C","occurredAt":"2026-09-09T19:24:00+08:00","recordedAt":"2026-09-09T20:24:00+08:00","workerName":"示範工作員甲（合成）","coverage":"VISITED_NO_FINDING","assessment":"NO_INDICATION","contactOutcome":"CONTACTED","evidence":[]},{"isSynthetic":true,"provisional":true,"id":"observation-bldg-yu-an-f4-D","visitId":"visit-yu-an-2026-09-09","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f4","unitId":"bldg-yu-an-f4-D","occurredAt":"2026-09-09T19:25:00+08:00","recordedAt":"2026-09-09T20:25:00+08:00","workerName":"示範工作員甲（合成）","coverage":"PARTIAL","assessment":"NOT_UPDATED","contactOutcome":"UNKNOWN","evidence":[]},{"isSynthetic":true,"provisional":true,"id":"observation-bldg-yu-an-f6-A","visitId":"visit-yu-an-2026-09-09","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f6","unitId":"bldg-yu-an-f6-A","occurredAt":"2026-09-09T19:26:00+08:00","recordedAt":"2026-09-09T20:26:00+08:00","workerName":"示範工作員甲（合成）","coverage":"VISITED_NO_FINDING","assessment":"NO_INDICATION","contactOutcome":"CONTACTED","evidence":[]},{"isSynthetic":true,"provisional":true,"id":"observation-bldg-yu-an-f6-B","visitId":"visit-yu-an-2026-09-09","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f6","unitId":"bldg-yu-an-f6-B","occurredAt":"2026-09-09T19:27:00+08:00","recordedAt":"2026-09-09T20:27:00+08:00","workerName":"示範工作員甲（合成）","coverage":"VISITED_NO_FINDING","assessment":"NO_INDICATION","contactOutcome":"CONTACTED","evidence":[]},{"isSynthetic":true,"provisional":true,"id":"observation-hoi-king-2a","visitId":"visit-hoi-king-2026-09-08","buildingId":"bldg-hoi-king","floorId":"bldg-hoi-king-f2","unitId":"bldg-hoi-king-f2-A","occurredAt":"2026-09-08T18:45:00+08:00","recordedAt":"2026-09-08T20:15:00+08:00","workerName":"示範工作員乙（合成）","coverage":"VISITED_NO_FINDING","assessment":"NOT_UPDATED","contactOutcome":"CONTACTED","evidence":[],"note":"合成示例：已探訪但本次未記錄發現。"},{"isSynthetic":true,"provisional":true,"id":"observation-hoi-king-2b","visitId":"visit-hoi-king-2026-09-08","buildingId":"bldg-hoi-king","floorId":"bldg-hoi-king-f2","unitId":"bldg-hoi-king-f2-B","occurredAt":"2026-09-08T18:44:00+08:00","recordedAt":"2026-09-08T20:14:00+08:00","workerName":"示範工作員乙（合成）","coverage":"VISITED_NO_FINDING","assessment":"NO_INDICATION","contactOutcome":"CONTACTED","evidence":[]},{"isSynthetic":true,"provisional":true,"id":"observation-duk-cheong-entry","visitId":"visit-duk-cheong-2026-09-07","buildingId":"bldg-duk-cheong","occurredAt":"2026-09-07T18:45:00+08:00","recordedAt":"2026-09-07T20:15:00+08:00","workerName":"示範工作員丙（合成）","coverage":"INACCESSIBLE","contactOutcome":"NOT_ATTEMPTED","evidence":["合成示例：入口未能進入。"],"followUp":{"action":"合成示例：與同事討論是否再訪","status":"OPEN"}},{"isSynthetic":true,"provisional":true,"id":"demo-paper-housing","visitId":"demo-paper-visit-0910","buildingId":"bldg-yu-an","floorId":"bldg-yu-an-f5","unitId":"bldg-yu-an-f5-B","occurredAt":"2026-09-10","recordedAt":"2026-09-11T09:00:00+08:00","workerName":"演示工作員乙","coverage":"ATTEMPTED","contactOutcome":"CONTACTED","assessment":"NOT_UPDATED","sourceType":"RESIDENT_REPORT","note":"合成示例：住戶表示業主可能收回單位。具體安排和通知日期未確認。","evidence":["合成居民口述，未見書面通知"],"paperRef":"DEMO-0910-01","paperLine":"1","followUp":{"action":"再聯絡住戶，確認搬遷安排及需要的住屋支援","status":"OPEN","category":"HOUSING_CHANGE","assignee":"演示工作員乙","timingNote":"「明年二月」為示範原話，年份及日期待核實"}},{"isSynthetic":true,"provisional":true,"id":"demo-paper-health","visitId":"demo-paper-visit-0910","buildingId":"bldg-hoi-king","occurredAt":"2026-09-10","recordedAt":"2026-09-11T09:05:00+08:00","workerName":"演示工作員乙","coverage":"PARTIAL","contactOutcome":"CONTACTED","assessment":"NOT_UPDATED","sourceType":"RESIDENT_REPORT","note":"合成示例：街坊提到腳部不適及走路困難。只記錄表述，不推定病名。","evidence":["合成居民口述"],"paperRef":"DEMO-0910-02","paperLine":"1","followUp":{"action":"聯絡中心護士同事，確認可提供的關懷安排","status":"OPEN","category":"HEALTH_SUPPORT","assignee":"演示工作員乙","timingNote":"翌日午後（實際日期及到場安排待確認）"}},{"isSynthetic":true,"provisional":true,"id":"demo-paper-invite","visitId":"demo-paper-visit-0910","buildingId":"bldg-hoi-king","occurredAt":"2026-09-10","recordedAt":"2026-09-11T09:10:00+08:00","workerName":"演示工作員乙","coverage":"PARTIAL","contactOutcome":"CONTACTED","assessment":"NOT_UPDATED","sourceType":"STAFF_OBSERVATION","note":"合成示例：已介紹社區客廳服務，街坊有興趣了解；未表示已入會。","evidence":[],"paperRef":"DEMO-0910-02","paperLine":"2","followUp":{"action":"確認街坊到訪意願及是否需要協助前來","status":"OPEN","category":"SERVICE_INVITATION","timingNote":"有口頭邀約，未確認到場"}}]}</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="25" customHeight="1">
